--- a/data/processed/positivacao/2023-07_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-07_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25205,7 +25205,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B957" t="inlineStr"/>
@@ -36479,7 +36479,7 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr"/>
@@ -65657,7 +65657,7 @@
     <row r="2514">
       <c r="A2514" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2514" t="inlineStr"/>
@@ -67302,12 +67302,12 @@
       <c r="A2578" t="inlineStr"/>
       <c r="B2578" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 13.277,68
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 13.277,68
 Vendedor 18 - LOJA: positivou 136 cliente(s), não positivou 716 cliente(s) - Total vendido: R$ 68.291,96
-Vendedor 3 - FERNANDA: positivou 100 cliente(s), não positivou 333 cliente(s) - Total vendido: R$ 142.528,72
-Vendedor 4 - DANIELA: positivou 85 cliente(s), não positivou 585 cliente(s) - Total vendido: R$ 41.368,11
+Vendedor 3 - VENDEDOR 03: positivou 100 cliente(s), não positivou 333 cliente(s) - Total vendido: R$ 142.528,72
+Vendedor 4 - VENDEDOR 04: positivou 85 cliente(s), não positivou 585 cliente(s) - Total vendido: R$ 41.368,11
 Vendedor 5 - SITE: positivou 6 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 388,43
-Vendedor 8 - RAFAEL: positivou 1 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 72,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 1 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 72,00</t>
         </is>
       </c>
       <c r="C2578" t="inlineStr"/>
